--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/CFGProcess.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/CFGProcess.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16350" windowHeight="10480"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>{.ruleDesc}</t>
   </si>
   <si>
-    <t>{.disabled}</t>
+    <t>{.disabledName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -771,6 +771,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1024,18 +1031,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="15.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="11.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="14.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="11.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="11.4545454545455" customWidth="1"/>
-    <col min="7" max="7" width="10.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.0909090909091" customWidth="1"/>
-    <col min="9" max="9" width="13.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="12.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="15.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="11.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="14.4583333333333" customWidth="1"/>
+    <col min="4" max="4" width="11.6333333333333" customWidth="1"/>
+    <col min="5" max="5" width="20.375" customWidth="1"/>
+    <col min="6" max="6" width="11.4583333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="9" max="9" width="21.625" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
